--- a/data/nzd0164/nzd0164.xlsx
+++ b/data/nzd0164/nzd0164.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E337"/>
+  <dimension ref="A1:E338"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7509,6 +7509,27 @@
         <v>342.74</v>
       </c>
       <c r="E337" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:05:44+00:00</t>
+        </is>
+      </c>
+      <c r="B338" t="n">
+        <v>339.78</v>
+      </c>
+      <c r="C338" t="n">
+        <v>335.65</v>
+      </c>
+      <c r="D338" t="n">
+        <v>337.47</v>
+      </c>
+      <c r="E338" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -7525,7 +7546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B379"/>
+  <dimension ref="A1:B380"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11318,6 +11339,16 @@
       </c>
       <c r="B379" t="n">
         <v>-0.4</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B380" t="n">
+        <v>0.52</v>
       </c>
     </row>
   </sheetData>
@@ -11486,28 +11517,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.06419663064130636</v>
+        <v>-0.0658496863791139</v>
       </c>
       <c r="J2" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K2" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01184426765835611</v>
+        <v>0.01251930227048992</v>
       </c>
       <c r="M2" t="n">
-        <v>3.399720104189537</v>
+        <v>3.397805999455507</v>
       </c>
       <c r="N2" t="n">
-        <v>18.35632080124144</v>
+        <v>18.32433330629914</v>
       </c>
       <c r="O2" t="n">
-        <v>4.284427709886286</v>
+        <v>4.280693087141279</v>
       </c>
       <c r="P2" t="n">
-        <v>344.232314280989</v>
+        <v>344.2497521363724</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -11564,28 +11595,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1521265998134756</v>
+        <v>-0.1517460603250527</v>
       </c>
       <c r="J3" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K3" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04592626970774394</v>
+        <v>0.04598918888469961</v>
       </c>
       <c r="M3" t="n">
-        <v>4.023397081495705</v>
+        <v>4.013119560642428</v>
       </c>
       <c r="N3" t="n">
-        <v>25.66699767254772</v>
+        <v>25.59202589556313</v>
       </c>
       <c r="O3" t="n">
-        <v>5.066260718966969</v>
+        <v>5.058856184510796</v>
       </c>
       <c r="P3" t="n">
-        <v>339.0110790342787</v>
+        <v>339.007064776069</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -11642,28 +11673,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.06197768014027313</v>
+        <v>0.06266417969561908</v>
       </c>
       <c r="J4" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K4" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="L4" t="n">
-        <v>0.003104554136919679</v>
+        <v>0.003193902507566349</v>
       </c>
       <c r="M4" t="n">
-        <v>6.203144141843502</v>
+        <v>6.187763592059777</v>
       </c>
       <c r="N4" t="n">
-        <v>65.85139741381448</v>
+        <v>65.65987012418547</v>
       </c>
       <c r="O4" t="n">
-        <v>8.114887393785233</v>
+        <v>8.103077817976665</v>
       </c>
       <c r="P4" t="n">
-        <v>334.6871290419492</v>
+        <v>334.6798872534886</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -11701,7 +11732,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E337"/>
+  <dimension ref="A1:E338"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20803,6 +20834,33 @@
         </is>
       </c>
     </row>
+    <row r="338">
+      <c r="A338" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:05:44+00:00</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>-36.757760970090104,175.75744184530538</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>-36.75787232827023,175.75651603488132</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>-36.758214544633766,175.75569728145706</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0164/nzd0164.xlsx
+++ b/data/nzd0164/nzd0164.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E338"/>
+  <dimension ref="A1:E339"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7532,6 +7532,27 @@
       <c r="E338" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-02 22:05:53+00:00</t>
+        </is>
+      </c>
+      <c r="B339" t="n">
+        <v>338.1</v>
+      </c>
+      <c r="C339" t="n">
+        <v>333.62</v>
+      </c>
+      <c r="D339" t="n">
+        <v>332.25</v>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -7546,7 +7567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B380"/>
+  <dimension ref="A1:B381"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11349,6 +11370,16 @@
       </c>
       <c r="B380" t="n">
         <v>0.52</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>2026-02-02 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B381" t="n">
+        <v>0.32</v>
       </c>
     </row>
   </sheetData>
@@ -11517,28 +11548,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.0658496863791139</v>
+        <v>-0.0684810382021734</v>
       </c>
       <c r="J2" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K2" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01251930227048992</v>
+        <v>0.01357098919056177</v>
       </c>
       <c r="M2" t="n">
-        <v>3.397805999455507</v>
+        <v>3.400749516254203</v>
       </c>
       <c r="N2" t="n">
-        <v>18.32433330629914</v>
+        <v>18.32730385233513</v>
       </c>
       <c r="O2" t="n">
-        <v>4.280693087141279</v>
+        <v>4.281040043299658</v>
       </c>
       <c r="P2" t="n">
-        <v>344.2497521363724</v>
+        <v>344.2775889576364</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -11595,28 +11626,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1517460603250527</v>
+        <v>-0.1525701376127235</v>
       </c>
       <c r="J3" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K3" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04598918888469961</v>
+        <v>0.04674533484123433</v>
       </c>
       <c r="M3" t="n">
-        <v>4.013119560642428</v>
+        <v>4.005811459408067</v>
       </c>
       <c r="N3" t="n">
-        <v>25.59202589556313</v>
+        <v>25.52191847220389</v>
       </c>
       <c r="O3" t="n">
-        <v>5.058856184510796</v>
+        <v>5.051922255162276</v>
       </c>
       <c r="P3" t="n">
-        <v>339.007064776069</v>
+        <v>339.0157826115038</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -11673,28 +11704,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.06266417969561908</v>
+        <v>0.06023347711599236</v>
       </c>
       <c r="J4" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K4" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L4" t="n">
-        <v>0.003193902507566349</v>
+        <v>0.002968598567041347</v>
       </c>
       <c r="M4" t="n">
-        <v>6.187763592059777</v>
+        <v>6.182751268381684</v>
       </c>
       <c r="N4" t="n">
-        <v>65.65987012418547</v>
+        <v>65.51440618601661</v>
       </c>
       <c r="O4" t="n">
-        <v>8.103077817976665</v>
+        <v>8.09409699633113</v>
       </c>
       <c r="P4" t="n">
-        <v>334.6798872534886</v>
+        <v>334.7056014254446</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -11732,7 +11763,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E338"/>
+  <dimension ref="A1:E339"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20861,6 +20892,33 @@
         </is>
       </c>
     </row>
+    <row r="339">
+      <c r="A339" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-02 22:05:53+00:00</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>-36.757746189769634,175.75743780541646</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>-36.757855141580706,175.7565082726443</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>-36.75817288518864,175.75567017884094</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0164/nzd0164.xlsx
+++ b/data/nzd0164/nzd0164.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E339"/>
+  <dimension ref="A1:E340"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7553,6 +7553,27 @@
       <c r="E339" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:05:37+00:00</t>
+        </is>
+      </c>
+      <c r="B340" t="n">
+        <v>339.6</v>
+      </c>
+      <c r="C340" t="n">
+        <v>334.58</v>
+      </c>
+      <c r="D340" t="n">
+        <v>329.21</v>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -7567,7 +7588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B381"/>
+  <dimension ref="A1:B382"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11380,6 +11401,16 @@
       </c>
       <c r="B381" t="n">
         <v>0.32</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B382" t="n">
+        <v>-0.42</v>
       </c>
     </row>
   </sheetData>
@@ -11548,28 +11579,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.0684810382021734</v>
+        <v>-0.07018175615794388</v>
       </c>
       <c r="J2" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="K2" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01357098919056177</v>
+        <v>0.01431655807542831</v>
       </c>
       <c r="M2" t="n">
-        <v>3.400749516254203</v>
+        <v>3.399110960023086</v>
       </c>
       <c r="N2" t="n">
-        <v>18.32730385233513</v>
+        <v>18.29722113312987</v>
       </c>
       <c r="O2" t="n">
-        <v>4.281040043299658</v>
+        <v>4.277525117767267</v>
       </c>
       <c r="P2" t="n">
-        <v>344.2775889576364</v>
+        <v>344.2956316516719</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -11626,28 +11657,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1525701376127235</v>
+        <v>-0.1528104815481122</v>
       </c>
       <c r="J3" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="K3" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04674533484123433</v>
+        <v>0.04717571034291623</v>
       </c>
       <c r="M3" t="n">
-        <v>4.005811459408067</v>
+        <v>3.995336980467136</v>
       </c>
       <c r="N3" t="n">
-        <v>25.52191847220389</v>
+        <v>25.44711148619126</v>
       </c>
       <c r="O3" t="n">
-        <v>5.051922255162276</v>
+        <v>5.044513007832497</v>
       </c>
       <c r="P3" t="n">
-        <v>339.0157826115038</v>
+        <v>339.0183323888345</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -11704,28 +11735,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.06023347711599236</v>
+        <v>0.05602396328330283</v>
       </c>
       <c r="J4" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="K4" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002968598567041347</v>
+        <v>0.002580085307119506</v>
       </c>
       <c r="M4" t="n">
-        <v>6.182751268381684</v>
+        <v>6.187323872318767</v>
       </c>
       <c r="N4" t="n">
-        <v>65.51440618601661</v>
+        <v>65.46805813219501</v>
       </c>
       <c r="O4" t="n">
-        <v>8.09409699633113</v>
+        <v>8.091233412292283</v>
       </c>
       <c r="P4" t="n">
-        <v>334.7056014254446</v>
+        <v>334.7502596063404</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -11763,7 +11794,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E339"/>
+  <dimension ref="A1:E340"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20919,6 +20950,33 @@
         </is>
       </c>
     </row>
+    <row r="340">
+      <c r="A340" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:05:37+00:00</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>-36.75775938648435,175.75744141246005</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>-36.75786326927634,175.75651194345545</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>-36.758148623745804,175.7556543949559</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0164/nzd0164.xlsx
+++ b/data/nzd0164/nzd0164.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E340"/>
+  <dimension ref="A1:E341"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7572,6 +7572,27 @@
         <v>329.21</v>
       </c>
       <c r="E340" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:05:50+00:00</t>
+        </is>
+      </c>
+      <c r="B341" t="n">
+        <v>341.32</v>
+      </c>
+      <c r="C341" t="n">
+        <v>335.34</v>
+      </c>
+      <c r="D341" t="n">
+        <v>330.85</v>
+      </c>
+      <c r="E341" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -7588,7 +7609,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B382"/>
+  <dimension ref="A1:B383"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11410,6 +11431,16 @@
         </is>
       </c>
       <c r="B382" t="n">
+        <v>-0.42</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B383" t="n">
         <v>-0.42</v>
       </c>
     </row>
@@ -11579,28 +11610,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.07018175615794388</v>
+        <v>-0.07083909261796485</v>
       </c>
       <c r="J2" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K2" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01431655807542831</v>
+        <v>0.01467231108591305</v>
       </c>
       <c r="M2" t="n">
-        <v>3.399110960023086</v>
+        <v>3.392338081692247</v>
       </c>
       <c r="N2" t="n">
-        <v>18.29722113312987</v>
+        <v>18.24701630550183</v>
       </c>
       <c r="O2" t="n">
-        <v>4.277525117767267</v>
+        <v>4.271652643357349</v>
       </c>
       <c r="P2" t="n">
-        <v>344.2956316516719</v>
+        <v>344.3026183706409</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -11657,28 +11688,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1528104815481122</v>
+        <v>-0.1525907180235313</v>
       </c>
       <c r="J3" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K3" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04717571034291623</v>
+        <v>0.04733620454479437</v>
       </c>
       <c r="M3" t="n">
-        <v>3.995336980467136</v>
+        <v>3.984534953758621</v>
       </c>
       <c r="N3" t="n">
-        <v>25.44711148619126</v>
+        <v>25.37267059921429</v>
       </c>
       <c r="O3" t="n">
-        <v>5.044513007832497</v>
+        <v>5.037129202156154</v>
       </c>
       <c r="P3" t="n">
-        <v>339.0183323888345</v>
+        <v>339.0159965591959</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -11735,28 +11766,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.05602396328330283</v>
+        <v>0.0528471844832361</v>
       </c>
       <c r="J4" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K4" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002580085307119506</v>
+        <v>0.002308303213949814</v>
       </c>
       <c r="M4" t="n">
-        <v>6.187323872318767</v>
+        <v>6.186227995392723</v>
       </c>
       <c r="N4" t="n">
-        <v>65.46805813219501</v>
+        <v>65.35983253520941</v>
       </c>
       <c r="O4" t="n">
-        <v>8.091233412292283</v>
+        <v>8.084542815472586</v>
       </c>
       <c r="P4" t="n">
-        <v>334.7502596063404</v>
+        <v>334.7840250553188</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -11794,7 +11825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E340"/>
+  <dimension ref="A1:E341"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20977,6 +21008,33 @@
         </is>
       </c>
     </row>
+    <row r="341">
+      <c r="A341" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:05:50+00:00</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>-36.75777451871697,175.75744554853839</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>-36.75786970370192,175.75651484951482</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>-36.758161712156074,175.75566290994524</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0164/nzd0164.xlsx
+++ b/data/nzd0164/nzd0164.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E341"/>
+  <dimension ref="A1:E343"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7595,6 +7595,48 @@
       <c r="E341" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:04:44+00:00</t>
+        </is>
+      </c>
+      <c r="B342" t="n">
+        <v>343.09</v>
+      </c>
+      <c r="C342" t="n">
+        <v>332.68</v>
+      </c>
+      <c r="D342" t="n">
+        <v>329.44</v>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:05:20+00:00</t>
+        </is>
+      </c>
+      <c r="B343" t="n">
+        <v>344.94</v>
+      </c>
+      <c r="C343" t="n">
+        <v>333.66</v>
+      </c>
+      <c r="D343" t="n">
+        <v>331.4</v>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -7609,7 +7651,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B383"/>
+  <dimension ref="A1:B385"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11442,6 +11484,26 @@
       </c>
       <c r="B383" t="n">
         <v>-0.42</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B384" t="n">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B385" t="n">
+        <v>-0.54</v>
       </c>
     </row>
   </sheetData>
@@ -11610,28 +11672,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.07083909261796485</v>
+        <v>-0.06894755332831043</v>
       </c>
       <c r="J2" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="K2" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01467231108591305</v>
+        <v>0.01407590488482469</v>
       </c>
       <c r="M2" t="n">
-        <v>3.392338081692247</v>
+        <v>3.38185520160214</v>
       </c>
       <c r="N2" t="n">
-        <v>18.24701630550183</v>
+        <v>18.16010893168596</v>
       </c>
       <c r="O2" t="n">
-        <v>4.271652643357349</v>
+        <v>4.261467931556679</v>
       </c>
       <c r="P2" t="n">
-        <v>344.3026183706409</v>
+        <v>344.2823494746328</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -11688,28 +11750,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1525907180235313</v>
+        <v>-0.1546852678319095</v>
       </c>
       <c r="J3" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="K3" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04733620454479437</v>
+        <v>0.04915482812058514</v>
       </c>
       <c r="M3" t="n">
-        <v>3.984534953758621</v>
+        <v>3.972850681218649</v>
       </c>
       <c r="N3" t="n">
-        <v>25.37267059921429</v>
+        <v>25.243821722715</v>
       </c>
       <c r="O3" t="n">
-        <v>5.037129202156154</v>
+        <v>5.024323011383225</v>
       </c>
       <c r="P3" t="n">
-        <v>339.0159965591959</v>
+        <v>339.0384319881188</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -11766,28 +11828,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0528471844832361</v>
+        <v>0.04604272816440953</v>
       </c>
       <c r="J4" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="K4" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002308303213949814</v>
+        <v>0.001770875670068173</v>
       </c>
       <c r="M4" t="n">
-        <v>6.186227995392723</v>
+        <v>6.186610417367846</v>
       </c>
       <c r="N4" t="n">
-        <v>65.35983253520941</v>
+        <v>65.17451930540214</v>
       </c>
       <c r="O4" t="n">
-        <v>8.084542815472586</v>
+        <v>8.073073721043437</v>
       </c>
       <c r="P4" t="n">
-        <v>334.7840250553188</v>
+        <v>334.8569134343045</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -11825,7 +11887,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E341"/>
+  <dimension ref="A1:E343"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21035,6 +21097,60 @@
         </is>
       </c>
     </row>
+    <row r="342">
+      <c r="A342" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:04:44+00:00</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>-36.75779009083984,175.75744980485342</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>-36.757847183211936,175.75650467830923</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>-36.758150459315594,175.75565558913107</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:05:20+00:00</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>-36.757806366787186,175.75745425354637</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>-36.7578554802347,175.75650842559477</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>-36.75816610156179,175.7556657655826</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0164/nzd0164.xlsx
+++ b/data/nzd0164/nzd0164.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E343"/>
+  <dimension ref="A1:E344"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7635,6 +7635,27 @@
         <v>331.4</v>
       </c>
       <c r="E343" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:04:54+00:00</t>
+        </is>
+      </c>
+      <c r="B344" t="n">
+        <v>347.22</v>
+      </c>
+      <c r="C344" t="n">
+        <v>334.95</v>
+      </c>
+      <c r="D344" t="n">
+        <v>333.98</v>
+      </c>
+      <c r="E344" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -7651,7 +7672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B385"/>
+  <dimension ref="A1:B386"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11504,6 +11525,16 @@
       </c>
       <c r="B385" t="n">
         <v>-0.54</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B386" t="n">
+        <v>-0.59</v>
       </c>
     </row>
   </sheetData>
@@ -11672,28 +11703,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.06894755332831043</v>
+        <v>-0.06614226575806692</v>
       </c>
       <c r="J2" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="K2" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01407590488482469</v>
+        <v>0.0130050305814744</v>
       </c>
       <c r="M2" t="n">
-        <v>3.38185520160214</v>
+        <v>3.385856592067536</v>
       </c>
       <c r="N2" t="n">
-        <v>18.16010893168596</v>
+        <v>18.17319292730396</v>
       </c>
       <c r="O2" t="n">
-        <v>4.261467931556679</v>
+        <v>4.263002806391753</v>
       </c>
       <c r="P2" t="n">
-        <v>344.2823494746328</v>
+        <v>344.252228287473</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -11750,28 +11781,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1546852678319095</v>
+        <v>-0.1546572025327488</v>
       </c>
       <c r="J3" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="K3" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04915482812058514</v>
+        <v>0.04944256564636884</v>
       </c>
       <c r="M3" t="n">
-        <v>3.972850681218649</v>
+        <v>3.961389790673474</v>
       </c>
       <c r="N3" t="n">
-        <v>25.243821722715</v>
+        <v>25.17023118357692</v>
       </c>
       <c r="O3" t="n">
-        <v>5.024323011383225</v>
+        <v>5.016994237945357</v>
       </c>
       <c r="P3" t="n">
-        <v>339.0384319881188</v>
+        <v>339.0381306428529</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -11828,28 +11859,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.04604272816440953</v>
+        <v>0.04480892122866219</v>
       </c>
       <c r="J4" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="K4" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001770875670068173</v>
+        <v>0.001687989107408305</v>
       </c>
       <c r="M4" t="n">
-        <v>6.186610417367846</v>
+        <v>6.175147797317902</v>
       </c>
       <c r="N4" t="n">
-        <v>65.17451930540214</v>
+        <v>64.99727856840066</v>
       </c>
       <c r="O4" t="n">
-        <v>8.073073721043437</v>
+        <v>8.062088970508864</v>
       </c>
       <c r="P4" t="n">
-        <v>334.8569134343045</v>
+        <v>334.8701611776107</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -11887,7 +11918,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E343"/>
+  <dimension ref="A1:E344"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21151,6 +21182,33 @@
         </is>
       </c>
     </row>
+    <row r="344">
+      <c r="A344" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:04:54+00:00</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>-36.75782642579218,175.7574597362627</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>-36.75786640182565,175.75651335824747</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>-36.758186691863834,175.75567916112223</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
